--- a/assets/template/formula_template.xlsx
+++ b/assets/template/formula_template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,9 +27,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="43">
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -108,6 +115,9 @@
     </r>
   </si>
   <si>
+    <t>Barcode</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -247,6 +257,9 @@
   </si>
   <si>
     <t>Enter the weighing unit of the formula.</t>
+  </si>
+  <si>
+    <t>Enter the formula Barcode.</t>
   </si>
   <si>
     <t>Enter the notes of the formula.</t>
@@ -1424,21 +1437,22 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="16.1142857142857" customWidth="1"/>
     <col min="2" max="2" width="16.447619047619" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="17.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="25.5714285714286" customWidth="1"/>
-    <col min="8" max="8" width="17.552380952381" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="31.1142857142857" customWidth="1"/>
-    <col min="11" max="11" width="18.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="18.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="17.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="25.5714285714286" customWidth="1"/>
+    <col min="9" max="9" width="17.552380952381" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="31.1142857142857" customWidth="1"/>
+    <col min="12" max="12" width="18.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1463,7 +1477,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -1472,276 +1486,291 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:11">
+    <row r="2" s="2" customFormat="1" spans="1:12">
       <c r="A2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="K2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="6">
         <v>1001</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="6">
+      <c r="I3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="6">
         <v>200</v>
       </c>
-      <c r="K3" s="6">
+      <c r="L3" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" s="6">
         <v>1001</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="F4" s="7"/>
       <c r="G4" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="6">
+        <v>19</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="6">
         <v>150</v>
       </c>
-      <c r="K4" s="6">
+      <c r="L4" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5" s="6">
         <v>1001</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="F5" s="7"/>
       <c r="G5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="6">
+        <v>19</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="6">
         <v>100</v>
       </c>
-      <c r="K5" s="6">
+      <c r="L5" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6" s="6">
         <v>1002</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="F6" s="7"/>
       <c r="G6" s="7" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="6">
+        <v>20</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7" s="6">
         <v>1002</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="7"/>
-      <c r="F7" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="F7" s="7"/>
       <c r="G7" s="7" t="s">
         <v>25</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="6">
+        <v>21</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="13" customHeight="1" spans="1:11">
+    <row r="8" ht="13" customHeight="1" spans="1:12">
       <c r="A8" s="6">
         <v>1002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="7"/>
-      <c r="F8" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="F8" s="7"/>
       <c r="G8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="6">
+        <v>22</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:11">
+    <row r="9" s="2" customFormat="1" spans="1:12">
       <c r="A9" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:12">
       <c r="A10" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
